--- a/outputs/Block2_Pipeline_Stage_Summary_v12.xlsx
+++ b/outputs/Block2_Pipeline_Stage_Summary_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Group</t>
   </si>
@@ -34,13 +34,7 @@
     <t>Election_Exams</t>
   </si>
   <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
     <t>Popular Vote</t>
-  </si>
-  <si>
-    <t>Senate Buckets</t>
   </si>
 </sst>
 </file>
@@ -398,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -426,58 +420,18 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>5.24749619700716</v>
+        <v>0.01193820542365915</v>
       </c>
       <c r="C2">
-        <v>4.925</v>
+        <v>0.01193820542365915</v>
       </c>
       <c r="D2">
-        <v>-0.3224961970071595</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>0.01193820542365915</v>
-      </c>
-      <c r="C3">
-        <v>0.01193820542365915</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>1.038416113387647</v>
-      </c>
-      <c r="C4">
-        <v>0.8</v>
-      </c>
-      <c r="D4">
-        <v>-0.2384161133876466</v>
-      </c>
-      <c r="E4">
-        <v>80</v>
-      </c>
-      <c r="F4">
         <v>5</v>
       </c>
     </row>
